--- a/content_forms/046_social_writer_application_form--content_forms.xlsx
+++ b/content_forms/046_social_writer_application_form--content_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>option 4</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>option a</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option_b</t>
+          <t>option b</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option_c</t>
+          <t>option c</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option_d</t>
+          <t>option d</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option_e</t>
+          <t>option e</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option_f</t>
+          <t>option f</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option_g</t>
+          <t>option g</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option_h</t>
+          <t>option h</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option_i</t>
+          <t>option i</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option_j</t>
+          <t>option j</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option_k</t>
+          <t>option k</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option_l</t>
+          <t>option l</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option_m</t>
+          <t>option m</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>referee_a</t>
+          <t>referee a</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>referee_b</t>
+          <t>referee b</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>referee_c</t>
+          <t>referee c</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>referee_d</t>
+          <t>referee d</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ref_1</t>
+          <t>ref 1</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ref_2</t>
+          <t>ref 2</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ref_3</t>
+          <t>ref 3</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>emergency_1</t>
+          <t>emergency 1</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>emergency_2</t>
+          <t>emergency 2</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>emergency_3</t>
+          <t>emergency 3</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>option_n</t>
+          <t>option n</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>option_o</t>
+          <t>option o</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>option_p</t>
+          <t>option p</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
